--- a/data/trans_dic/IP31KM15_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM15_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,64; 62,3</t>
+          <t>54,96; 73,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,67; 71,74</t>
+          <t>47,79; 63,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,61; 65,38</t>
+          <t>53,6; 65,38</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>55,14%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,33; 62,89</t>
+          <t>46,23; 58,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,22; 57,5</t>
+          <t>51,86; 64,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,39; 58,24</t>
+          <t>50,62; 59,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>48,64%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,58; 53,97</t>
+          <t>38,27; 53,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,51; 54,22</t>
+          <t>45,0; 58,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,03; 51,67</t>
+          <t>43,46; 54,22</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,62%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,12; 73,31</t>
+          <t>56,29; 68,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56,06; 69,01</t>
+          <t>59,9; 72,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,96; 68,9</t>
+          <t>60,33; 69,08</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,75%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,69; 59,45</t>
+          <t>51,94; 59,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,79; 57,96</t>
+          <t>54,64; 61,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,2; 57,72</t>
+          <t>54,21; 59,51</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>106</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63192</t>
+          <t>78309</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81897</t>
+          <t>65391</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>145090</t>
+          <t>143701</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54429; 71183</t>
+          <t>67538; 89714</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>67949; 98150</t>
+          <t>56681; 75825</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>129578; 164138</t>
+          <t>129448; 157894</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>155</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>105217</t>
+          <t>121554</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>127427</t>
+          <t>105540</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>232645</t>
+          <t>227093</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91808; 117051</t>
+          <t>106907; 134859</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>111920; 142317</t>
+          <t>93661; 117175</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>209853; 252551</t>
+          <t>208471; 245249</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>118</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82546</t>
+          <t>76110</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86073</t>
+          <t>80302</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168619</t>
+          <t>156412</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>48147; 101599</t>
+          <t>63728; 89595</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72334; 99262</t>
+          <t>69760; 91300</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>130069; 191854</t>
+          <t>139756; 174337</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>156</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>110904</t>
+          <t>104134</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>110195</t>
+          <t>109214</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>221100</t>
+          <t>213347</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>100557; 120604</t>
+          <t>93531; 113753</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>99408; 122360</t>
+          <t>98221; 118445</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>204955; 235525</t>
+          <t>199187; 228078</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>535</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>361860</t>
+          <t>380108</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>405593</t>
+          <t>360446</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>767453</t>
+          <t>740553</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>311478; 388284</t>
+          <t>356711; 407480</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>378260; 431631</t>
+          <t>337793; 380812</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>715739; 806798</t>
+          <t>707394; 776670</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM15_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM15_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman 2 yogures y/o 40 g de queso cada día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>63,72%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>59,5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>54,96; 73,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>47,79; 63,93</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53,6; 65,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>52,57%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>58,44%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>46,23; 58,32</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>51,86; 64,88</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>50,62; 59,55</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>45,71%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>51,79%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>48,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>38,27; 53,8</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>45,0; 58,89</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>43,46; 54,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>62,67%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>66,6%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>64,62%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>56,29; 68,46</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>59,9; 72,23</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>60,33; 69,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>55,34%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58,31%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>56,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>51,94; 59,33</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>54,64; 61,6</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>54,21; 59,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6372007437942201</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.551368485623371</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.5950485345431028</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>78309</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>65391</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>143701</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.5495506379657454</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.4779222022394821</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.5360291364267261</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>67538; 89714</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>56681; 75825</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>129448; 157894</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7299988121466122</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.6393476982324148</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.6538229682282396</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.5256588154813443</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.5844068515940344</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.5514203841908526</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>121554</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>105540</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>227093</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4623173678093493</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.5186295479997596</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.5062037385409146</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>106907; 134859</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93661; 117175</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>208471; 245249</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.583194776742077</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.6488332623837618</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5955048853852436</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4570592948518732</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5179497155237678</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4864172388123738</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>76110</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>80302</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>156412</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.382698579683265</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.4499556033584027</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.4346188765503557</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>63728; 89595</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>69760; 91300</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>139756; 174337</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5380350502863901</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.5888879102396477</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.5421601434358482</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.6266889728983298</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.6660212823478886</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6462249125471824</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>104134</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>109214</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>213347</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5628777954651066</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.5989882758154277</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.6033350589761624</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>93531; 113753</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>98221; 118445</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>199187; 228078</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6845784791311408</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.7223163667826998</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.6908449786227522</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1040</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.5534278688418931</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.5830503165329192</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.5674603474507062</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>380108</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>360446</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>740553</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.5193635760153495</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.5464069230718962</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.5420516225005888</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>356711; 407480</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>337793; 380812</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>707394; 776670</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.5932814819740828</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.6159926674253522</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.5951354530144641</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman 2 yogures y/o 40 g de queso cada día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>78309</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>65391</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>143701</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>67538</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>56681</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>129448</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>89714</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>75825</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>157894</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>169</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>121554</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>105540</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>227093</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>106907</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>93661</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>208471</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>134859</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>117175</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>245249</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>118</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>76110</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>80302</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>156412</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>63728</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>69760</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>139756</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>89595</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>91300</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>174337</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>142</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>156</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>104134</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>109214</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>213347</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>93531</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>98221</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>199187</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>113753</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>118445</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>228078</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>505</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>535</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>380108</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>360446</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>740553</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>356711</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>337793</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>707394</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>407480</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>380812</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>776670</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>